--- a/input_data/admin_data/COL/_clean/total-pre-COL.xlsx
+++ b/input_data/admin_data/COL/_clean/total-pre-COL.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="294">
   <si>
     <t>poptot</t>
   </si>
@@ -52,6 +52,855 @@
   </si>
   <si>
     <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>poptot</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>topavg</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>eff_tax_rate</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t/>
@@ -107,31 +956,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -160,7 +1009,7 @@
         <v>2014</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -187,7 +1036,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -214,7 +1063,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -241,7 +1090,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -268,7 +1117,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -295,7 +1144,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -322,7 +1171,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -349,7 +1198,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -376,7 +1225,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -403,7 +1252,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -430,7 +1279,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -457,7 +1306,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -484,7 +1333,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -511,7 +1360,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -538,7 +1387,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +1414,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -592,7 +1441,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -619,7 +1468,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -646,7 +1495,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +1522,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -687,31 +1536,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -740,7 +1589,7 @@
         <v>2023</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -767,7 +1616,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4">
@@ -794,7 +1643,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5">
@@ -821,7 +1670,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6">
@@ -848,7 +1697,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
@@ -875,7 +1724,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8">
@@ -902,7 +1751,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9">
@@ -929,7 +1778,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -956,7 +1805,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11">
@@ -983,7 +1832,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -1010,7 +1859,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1886,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14">
@@ -1064,7 +1913,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15">
@@ -1091,7 +1940,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16">
@@ -1118,7 +1967,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -1145,7 +1994,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18">
@@ -1172,7 +2021,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19">
@@ -1199,7 +2048,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20">
@@ -1226,7 +2075,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21">
@@ -1253,7 +2102,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -1267,31 +2116,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -1320,7 +2169,7 @@
         <v>2015</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1347,7 +2196,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -1374,7 +2223,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -1401,7 +2250,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -1428,7 +2277,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -1455,7 +2304,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -1482,7 +2331,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1509,7 +2358,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -1536,7 +2385,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -1563,7 +2412,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -1590,7 +2439,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -1617,7 +2466,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1644,7 +2493,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -1671,7 +2520,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1698,7 +2547,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1725,7 +2574,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -1752,7 +2601,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -1779,7 +2628,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1806,7 +2655,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
@@ -1833,7 +2682,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
@@ -1860,7 +2709,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1874,31 +2723,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
@@ -1927,7 +2776,7 @@
         <v>2016</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -1954,7 +2803,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -1981,7 +2830,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -2008,7 +2857,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -2035,7 +2884,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -2062,7 +2911,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2938,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -2116,7 +2965,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -2143,7 +2992,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -2170,7 +3019,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -2197,7 +3046,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -2224,7 +3073,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -2251,7 +3100,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -2278,7 +3127,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -2305,7 +3154,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -2332,7 +3181,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -2359,7 +3208,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -2386,7 +3235,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20">
@@ -2413,7 +3262,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -2440,7 +3289,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22">
@@ -2467,7 +3316,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2481,31 +3330,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
@@ -2534,7 +3383,7 @@
         <v>2017</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3">
@@ -2561,7 +3410,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
@@ -2588,7 +3437,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -2615,7 +3464,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -2642,7 +3491,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
@@ -2669,7 +3518,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -2696,7 +3545,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
@@ -2723,7 +3572,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -2750,7 +3599,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -2777,7 +3626,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
@@ -2804,7 +3653,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
@@ -2831,7 +3680,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -2858,7 +3707,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
@@ -2885,7 +3734,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -2912,7 +3761,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -2939,7 +3788,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -2966,7 +3815,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
@@ -2993,7 +3842,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
@@ -3020,7 +3869,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
@@ -3047,7 +3896,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
@@ -3074,7 +3923,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -3088,31 +3937,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2">
@@ -3141,7 +3990,7 @@
         <v>2018</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
@@ -3168,7 +4017,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
@@ -3195,7 +4044,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
@@ -3222,7 +4071,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
@@ -3249,7 +4098,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -3276,7 +4125,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -3303,7 +4152,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9">
@@ -3330,7 +4179,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -3357,7 +4206,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3384,7 +4233,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +4260,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -3438,7 +4287,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14">
@@ -3465,7 +4314,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15">
@@ -3492,7 +4341,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
@@ -3519,7 +4368,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
@@ -3546,7 +4395,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18">
@@ -3573,7 +4422,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
@@ -3600,7 +4449,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3614,31 +4463,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>161</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>164</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2">
@@ -3667,7 +4516,7 @@
         <v>2019</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
@@ -3694,7 +4543,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
@@ -3721,7 +4570,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5">
@@ -3748,7 +4597,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
@@ -3775,7 +4624,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
@@ -3802,7 +4651,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
@@ -3829,7 +4678,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9">
@@ -3856,7 +4705,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -3883,7 +4732,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3910,7 +4759,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -3937,7 +4786,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -3964,7 +4813,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
@@ -3991,7 +4840,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15">
@@ -4018,7 +4867,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">
@@ -4045,7 +4894,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17">
@@ -4072,7 +4921,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
@@ -4099,7 +4948,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -4126,7 +4975,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20">
@@ -4153,7 +5002,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -4167,31 +5016,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>189</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>192</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2">
@@ -4220,7 +5069,7 @@
         <v>2020</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
@@ -4247,7 +5096,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
@@ -4274,7 +5123,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
@@ -4301,7 +5150,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
@@ -4328,7 +5177,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -4355,7 +5204,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
@@ -4382,7 +5231,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -4409,7 +5258,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -4436,7 +5285,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -4463,7 +5312,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -4490,7 +5339,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -4517,7 +5366,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
@@ -4544,7 +5393,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -4571,7 +5420,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
@@ -4598,7 +5447,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
@@ -4625,7 +5474,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
@@ -4652,7 +5501,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4666,31 +5515,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>212</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>214</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>215</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>216</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>218</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2">
@@ -4719,7 +5568,7 @@
         <v>2021</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3">
@@ -4746,7 +5595,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
@@ -4773,7 +5622,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
@@ -4800,7 +5649,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
@@ -4827,7 +5676,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
@@ -4854,7 +5703,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
@@ -4881,7 +5730,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
@@ -4908,7 +5757,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +5784,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -4962,7 +5811,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12">
@@ -4989,7 +5838,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13">
@@ -5016,7 +5865,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
@@ -5043,7 +5892,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15">
@@ -5070,7 +5919,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16">
@@ -5097,7 +5946,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17">
@@ -5124,7 +5973,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18">
@@ -5151,7 +6000,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -5165,31 +6014,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>240</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>241</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>242</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>243</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>244</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
@@ -5218,7 +6067,7 @@
         <v>2022</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3">
@@ -5245,7 +6094,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -5272,7 +6121,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
@@ -5299,7 +6148,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
@@ -5326,7 +6175,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -5353,7 +6202,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
@@ -5380,7 +6229,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
@@ -5407,7 +6256,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -5434,7 +6283,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -5461,7 +6310,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
@@ -5488,7 +6337,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
@@ -5515,7 +6364,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
@@ -5542,7 +6391,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15">
@@ -5569,7 +6418,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16">
@@ -5596,7 +6445,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17">
@@ -5623,7 +6472,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18">
@@ -5650,7 +6499,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19">
@@ -5677,7 +6526,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20">
@@ -5704,7 +6553,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/input_data/admin_data/COL/_clean/total-pre-COL.xlsx
+++ b/input_data/admin_data/COL/_clean/total-pre-COL.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="294">
   <si>
     <t>poptot</t>
   </si>
@@ -956,31 +956,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -1009,7 +1009,7 @@
         <v>2014</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>34</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>35</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>36</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>37</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>39</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21">
@@ -2116,31 +2116,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>48</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -2169,7 +2169,7 @@
         <v>2015</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>50</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>54</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>55</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>56</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>59</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>63</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>64</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>65</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -2723,31 +2723,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>76</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -2776,7 +2776,7 @@
         <v>2016</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>80</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>86</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>89</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>91</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>96</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>98</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
-        <v>99</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -3330,31 +3330,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>106</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>108</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -3383,7 +3383,7 @@
         <v>2017</v>
       </c>
       <c r="I2" t="s">
-        <v>109</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>110</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>112</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>113</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>114</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>115</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>116</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>117</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>118</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>120</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>121</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>122</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>123</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>124</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>125</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>127</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
-        <v>128</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
-        <v>129</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -3937,31 +3937,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>130</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>137</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>138</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -3990,7 +3990,7 @@
         <v>2018</v>
       </c>
       <c r="I2" t="s">
-        <v>139</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>140</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>141</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>142</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>143</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>144</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>145</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>146</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>147</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>148</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>149</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>150</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>151</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>152</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>153</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>154</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>155</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>156</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -4463,31 +4463,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>158</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>161</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>163</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>165</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -4516,7 +4516,7 @@
         <v>2019</v>
       </c>
       <c r="I2" t="s">
-        <v>166</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>167</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>168</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>169</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>170</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>171</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>173</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>174</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>175</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>176</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>177</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>178</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>180</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>181</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>182</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>183</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>184</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -5016,31 +5016,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>187</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>188</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -5069,7 +5069,7 @@
         <v>2020</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>195</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>197</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>198</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>199</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>200</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>201</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>202</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>204</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>207</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>209</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>210</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -5515,31 +5515,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>214</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>217</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -5568,7 +5568,7 @@
         <v>2021</v>
       </c>
       <c r="I2" t="s">
-        <v>220</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>222</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>223</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>225</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>226</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>227</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>228</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>230</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>235</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -6014,31 +6014,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="G1" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="H1" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="I1" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
@@ -6067,7 +6067,7 @@
         <v>2022</v>
       </c>
       <c r="I2" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>253</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/input_data/admin_data/COL/_clean/total-pre-COL.xlsx
+++ b/input_data/admin_data/COL/_clean/total-pre-COL.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="294">
   <si>
     <t>poptot</t>
   </si>
